--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>hora_local_es_txt</t>
+          <t>hora_local_txt</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -41951,7 +41951,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Temporada de La Liga en formato "2025-26" (ago-may).</t>
+          <t>Temporada en formato "2025-26" (ago-may).</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -42007,7 +42007,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>hora_local_es_txt</t>
+          <t>hora_local_txt</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -42017,12 +42017,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Hora de inicio en Espana peninsular (Europe/Madrid), formato HH:MM. Vacia = no publicada.</t>
+          <t>Hora de inicio en hora local del pais de la liga, formato HH:MM. Vacia = no publicada.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Columna Time de football-data.co.uk viene en hora de Reino Unido; se convierte a Espana (+1 h, ambos cambian horario de verano el mismo dia).</t>
+          <t>Columna Time de football-data.co.uk viene en hora de Reino Unido; se convierte a la hora local de la liga (zona horaria del pais).</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Descarga automatica con generar_bbdd_laliga.py.</t>
+          <t>Descarga automatica con generar_bbdd.py.</t>
         </is>
       </c>
     </row>
@@ -42271,7 +42271,7 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Volver a correr generar_bbdd_laliga.py: descarga los CSV de las temporadas configuradas y regenera el Excel completo.</t>
+          <t>Volver a correr generar_bbdd.py: descarga los CSV de las temporadas configuradas y regenera el Excel completo de cada liga.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -42235,7 +42235,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>421 partidos (2025-26: 380 partidos, 2026-27: 41 partidos). 28 columnas. Cargado el 12/09/2026.</t>
+          <t>421 partidos (2025-26: 380 partidos, 2026-27: 41 partidos). 28 columnas. Cargado el 13/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -42235,7 +42235,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>421 partidos (2025-26: 380 partidos, 2026-27: 41 partidos). 28 columnas. Cargado el 13/09/2026.</t>
+          <t>421 partidos (2025-26: 380 partidos, 2026-27: 41 partidos). 28 columnas. Cargado el 14/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$422</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$432</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB422"/>
+  <dimension ref="A1:AB432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -41877,8 +41877,988 @@
         <v>1</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q423" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S423" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U423" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W423" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X423" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB423" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P424" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q424" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S424" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T424" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U424" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W424" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X424" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB424" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q425" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S425" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U425" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W425" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB425" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q426" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R426" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S426" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U426" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V426" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W426" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X426" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y426" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z426" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB426" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O427" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q427" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S427" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U427" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W427" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q428" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R428" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S428" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W428" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X428" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I429" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O429" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P429" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q429" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S429" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T429" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W429" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB429" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q430" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S430" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U430" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W430" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y430" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB430" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q431" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U431" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W431" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB431" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q432" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="S432" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="U432" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V432" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W432" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB432" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB422"/>
+  <autoFilter ref="A1:AB432"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42235,7 +43215,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>421 partidos (2025-26: 380 partidos, 2026-27: 41 partidos). 28 columnas. Cargado el 14/09/2026.</t>
+          <t>431 partidos (2025-26: 380 partidos, 2026-27: 51 partidos). 28 columnas. Cargado el 15/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -43215,7 +43215,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>431 partidos (2025-26: 380 partidos, 2026-27: 51 partidos). 28 columnas. Cargado el 15/09/2026.</t>
+          <t>431 partidos (2025-26: 380 partidos, 2026-27: 51 partidos). 28 columnas. Cargado el 16/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$440</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB432"/>
+  <dimension ref="A1:AB440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -42857,8 +42857,792 @@
         <v>0</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q433" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W433" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y433" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB433" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q434" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S434" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U434" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V434" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W434" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z434" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB434" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P435" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q435" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T435" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W435" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y435" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB435" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K436" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P436" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q436" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="R436" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S436" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U436" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W436" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB436" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q437" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S437" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U437" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W437" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X437" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z437" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB437" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I438" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K438" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O438" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P438" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q438" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="R438" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S438" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U438" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W438" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y438" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB438" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q439" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R439" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S439" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T439" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U439" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V439" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W439" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X439" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB439" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P440" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q440" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R440" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T440" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U440" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V440" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W440" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X440" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB440" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB432"/>
+  <autoFilter ref="A1:AB440"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43215,7 +43999,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>431 partidos (2025-26: 380 partidos, 2026-27: 51 partidos). 28 columnas. Cargado el 16/09/2026.</t>
+          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 18/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -43999,7 +43999,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 18/09/2026.</t>
+          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 19/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -43999,7 +43999,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 19/09/2026.</t>
+          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 20/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$440</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$459</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB440"/>
+  <dimension ref="A1:AB459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -43641,8 +43641,1870 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I441" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J441" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P441" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q441" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R441" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S441" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T441" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U441" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V441" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W441" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X441" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA441" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB441" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q442" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R442" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S442" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U442" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V442" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W442" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X442" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y442" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB442" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R443" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S443" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W443" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X443" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y443" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB443" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P444" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q444" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R444" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S444" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T444" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W444" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X444" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z444" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB444" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I445" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P445" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q445" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R445" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="S445" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T445" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V445" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W445" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X445" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB445" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q446" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R446" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S446" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T446" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U446" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V446" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W446" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X446" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y446" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z446" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB446" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q447" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R447" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S447" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W447" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="X447" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB447" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J448" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M448" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q448" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R448" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S448" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T448" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U448" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V448" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W448" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X448" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA448" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB448" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q449" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R449" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W449" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X449" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB449" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I450" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O450" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P450" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q450" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R450" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S450" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T450" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U450" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V450" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W450" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X450" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB450" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q451" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R451" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S451" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T451" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U451" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W451" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X451" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y451" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z451" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB451" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q452" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R452" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="S452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T452" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V452" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W452" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X452" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB452" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P453" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q453" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R453" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S453" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U453" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W453" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X453" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z453" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB453" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P454" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q454" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R454" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S454" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T454" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U454" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V454" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W454" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X454" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y454" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA454" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB454" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q455" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R455" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S455" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V455" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W455" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="X455" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y455" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z455" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB455" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O456" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P456" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q456" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R456" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S456" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T456" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U456" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V456" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W456" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X456" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB456" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K457" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P457" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q457" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R457" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S457" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U457" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V457" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W457" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X457" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB457" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P458" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q458" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R458" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S458" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U458" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V458" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W458" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X458" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y458" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z458" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB458" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I459" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M459" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O459" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P459" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q459" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R459" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S459" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T459" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U459" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V459" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W459" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X459" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y459" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z459" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB459" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB440"/>
+  <autoFilter ref="A1:AB459"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43999,7 +45861,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>439 partidos (2025-26: 380 partidos, 2026-27: 59 partidos). 28 columnas. Cargado el 20/09/2026.</t>
+          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 17/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -45861,7 +45861,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 17/10/2026.</t>
+          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 18/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -45861,7 +45861,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 18/10/2026.</t>
+          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 19/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$459</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB459"/>
+  <dimension ref="A1:AB469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -45503,8 +45503,988 @@
         <v>1</v>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q460" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R460" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S460" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T460" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U460" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V460" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W460" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X460" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB460" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q461" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R461" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T461" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U461" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V461" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W461" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X461" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z461" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB461" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R462" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S462" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V462" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W462" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X462" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z462" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB462" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I463" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M463" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O463" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P463" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q463" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R463" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S463" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T463" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V463" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W463" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X463" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y463" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB463" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q464" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R464" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T464" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U464" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V464" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W464" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X464" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB464" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q465" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R465" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S465" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U465" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V465" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W465" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X465" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB465" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I466" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M466" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P466" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q466" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R466" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S466" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T466" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V466" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W466" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X466" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y466" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z466" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB466" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M467" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O467" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P467" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q467" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R467" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S467" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T467" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U467" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V467" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W467" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="X467" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y467" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB467" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I468" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O468" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P468" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q468" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R468" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S468" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T468" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U468" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W468" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X468" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB468" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P469" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q469" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R469" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S469" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T469" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U469" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V469" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W469" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X469" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y469" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z469" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB469" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB459"/>
+  <autoFilter ref="A1:AB469"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45861,7 +46841,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>458 partidos (2025-26: 380 partidos, 2026-27: 78 partidos). 28 columnas. Cargado el 19/10/2026.</t>
+          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 20/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -46841,7 +46841,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 20/10/2026.</t>
+          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$470</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB469"/>
+  <dimension ref="A1:AB470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46483,8 +46483,106 @@
         <v>0</v>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L470" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P470" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q470" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R470" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S470" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T470" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U470" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V470" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W470" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X470" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA470" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB470" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB469"/>
+  <autoFilter ref="A1:AB470"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46841,7 +46939,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 21/10/2026.</t>
+          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 22/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB470"/>
+  <dimension ref="A1:AB469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46483,106 +46483,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" s="2" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="B470" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C470" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="D470" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F470" s="2" t="inlineStr">
-        <is>
-          <t>Levante</t>
-        </is>
-      </c>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="H470" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L470" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P470" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q470" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R470" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="S470" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T470" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U470" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V470" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W470" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X470" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA470" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB470" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB470"/>
+  <autoFilter ref="A1:AB469"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46939,7 +46841,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -46939,7 +46939,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 23/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -46939,7 +46939,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 23/10/2026.</t>
+          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 24/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -46939,7 +46939,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 24/10/2026.</t>
+          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 25/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -46939,7 +46939,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 25/10/2026.</t>
+          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 26/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$480</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB470"/>
+  <dimension ref="A1:AB480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46581,8 +46581,988 @@
         <v>1</v>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J471" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M471" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q471" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R471" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S471" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T471" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U471" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W471" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X471" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA471" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB471" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M472" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O472" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q472" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R472" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S472" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T472" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W472" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X472" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z472" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB472" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I473" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J473" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K473" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L473" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M473" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P473" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q473" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R473" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S473" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T473" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U473" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V473" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W473" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X473" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y473" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z473" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA473" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB473" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J474" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M474" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O474" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P474" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q474" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R474" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S474" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T474" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U474" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V474" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W474" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X474" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y474" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z474" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA474" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB474" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K475" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P475" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q475" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R475" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S475" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T475" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U475" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V475" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W475" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X475" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y475" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z475" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB475" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I476" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L476" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P476" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q476" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R476" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S476" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T476" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V476" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W476" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X476" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y476" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z476" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA476" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB476" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q477" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R477" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S477" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T477" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U477" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V477" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W477" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X477" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y477" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z477" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB477" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I478" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J478" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L478" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q478" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R478" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S478" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T478" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U478" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V478" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W478" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X478" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y478" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z478" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB478" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I479" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O479" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P479" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q479" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R479" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S479" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T479" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U479" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V479" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W479" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X479" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y479" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z479" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB479" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K480" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O480" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q480" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R480" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S480" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U480" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V480" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W480" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X480" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y480" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB480" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB470"/>
+  <autoFilter ref="A1:AB480"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46939,7 +47919,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>469 partidos (2025-26: 380 partidos, 2026-27: 89 partidos). 28 columnas. Cargado el 26/10/2026.</t>
+          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 27/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -47919,7 +47919,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 27/10/2026.</t>
+          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 28/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -47919,7 +47919,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 28/10/2026.</t>
+          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 29/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -47919,7 +47919,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 29/10/2026.</t>
+          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 30/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_laliga.xlsx
+++ b/datos/bbdd_laliga.xlsx
@@ -47919,7 +47919,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 30/10/2026.</t>
+          <t>479 partidos (2025-26: 380 partidos, 2026-27: 99 partidos). 28 columnas. Cargado el 31/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
